--- a/Result/profitability/4572.xlsx
+++ b/Result/profitability/4572.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM36"/>
+  <dimension ref="A1:AM37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5002,6 +5002,133 @@
         <v>115.1</v>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>4572</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>192</v>
+      </c>
+      <c r="D37" t="n">
+        <v>125</v>
+      </c>
+      <c r="E37" t="n">
+        <v>67</v>
+      </c>
+      <c r="F37" t="n">
+        <v>34.77</v>
+      </c>
+      <c r="G37" t="n">
+        <v>43</v>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>22.42%</t>
+        </is>
+      </c>
+      <c r="I37" t="n">
+        <v>4</v>
+      </c>
+      <c r="J37" t="n">
+        <v>47</v>
+      </c>
+      <c r="K37" t="n">
+        <v>37</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="M37" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="N37" t="n">
+        <v>37.7</v>
+      </c>
+      <c r="O37" t="n">
+        <v>1</v>
+      </c>
+      <c r="P37" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>0</v>
+      </c>
+      <c r="R37" t="n">
+        <v>0</v>
+      </c>
+      <c r="S37" t="n">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>0</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
+      </c>
+      <c r="V37" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W37" t="n">
+        <v>0.01999999999999991</v>
+      </c>
+      <c r="X37" t="n">
+        <v>0.02173913043478248</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>1.380000000000003</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>0.04132973944294704</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>-10.4</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>9.610000000000003</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0.3819554848966615</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK37" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>115.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
